--- a/sharedata/excel/Z-装备套装表(EquipSuitData).xlsx
+++ b/sharedata/excel/Z-装备套装表(EquipSuitData).xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\策划文档\配置表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ThroneOfAshes_Client\sharedata\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -33,9 +33,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="42">
-  <si>
-    <t>套装记录、名称、图标和排序待配置，不复制旧项目套装与资源编号。</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="43">
+  <si>
+    <t>临时套装样本，图标与排序为测试配置；红色加粗数据待正式数值与美术确认。</t>
   </si>
   <si>
     <t>装备套装表</t>
@@ -98,13 +98,10 @@
     <t>ref(IconData)</t>
   </si>
   <si>
-    <t>待配置</t>
-  </si>
-  <si>
-    <t>二件套与四件套分别配置；属性和值等长，属性与技能无对应效果时留空。</t>
-  </si>
-  <si>
-    <t>套装效果与技能记录待配置；套装技能引用公共技能表，不新建技能体系。</t>
+    <t>临时守卫套装</t>
+  </si>
+  <si>
+    <t>$Lang$临时守卫套装</t>
   </si>
   <si>
     <t>装备套装属性表</t>
@@ -159,6 +156,12 @@
   </si>
   <si>
     <t>ref(SkillData)</t>
+  </si>
+  <si>
+    <t>攻击比例</t>
+  </si>
+  <si>
+    <t>防御比例</t>
   </si>
 </sst>
 </file>
@@ -191,6 +194,13 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -340,13 +350,6 @@
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-      <b/>
-      <color rgb="FFFF0000"/>
     </font>
   </fonts>
   <fills count="34">
@@ -672,151 +675,151 @@
     </border>
   </borders>
   <cellStyleXfs count="50">
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -838,10 +841,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1327,8 +1330,8 @@
   </cols>
   <sheetData>
     <row r="1" ht="16.5" customHeight="1" spans="1:6">
-      <c r="A1" s="1" t="str">
-        <v>临时套装样本，图标与排序为测试配置；红色加粗数据待正式数值与美术确认。</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1420,21 +1423,21 @@
       </c>
       <c r="F6" s="3"/>
     </row>
-    <row r="7" ht="33.0" customHeight="1" spans="1:6">
+    <row r="7" ht="33" customHeight="1" spans="1:6">
       <c r="A7" s="5"/>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="6">
         <v>1</v>
       </c>
-      <c r="C7" s="6" t="str">
-        <v>临时守卫套装</v>
-      </c>
-      <c r="D7" s="6" t="str">
-        <v>$Lang$临时守卫套装</v>
-      </c>
-      <c r="E7" s="7" t="str">
-        <v>临时守卫套装</v>
-      </c>
-      <c r="F7" s="6" t="n">
+      <c r="C7" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="6">
         <v>1</v>
       </c>
     </row>
@@ -1451,7 +1454,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="17.4583333333333" customWidth="1"/>
     <col min="2" max="2" width="9.38333333333333" customWidth="1"/>
@@ -1463,9 +1466,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="16.5" customHeight="1" spans="1:7">
-      <c r="A1" s="1" t="str">
-        <v>临时二件/四件属性样本；同套装达四件时保留二件效果；技能不适用留空。</v>
-      </c>
+      <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -1474,9 +1475,7 @@
       <c r="G1" s="1"/>
     </row>
     <row r="2" ht="16.5" customHeight="1" spans="1:7">
-      <c r="A2" s="1" t="s">
-        <v>23</v>
-      </c>
+      <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1486,48 +1485,48 @@
     </row>
     <row r="3" ht="16.5" customHeight="1" spans="1:7">
       <c r="A3" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="4" ht="16.5" customHeight="1" spans="1:7">
       <c r="A4" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="5" ht="16.5" customHeight="1" spans="1:7">
@@ -1544,10 +1543,10 @@
         <v>14</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>15</v>
@@ -1561,52 +1560,52 @@
         <v>18</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="7" ht="16.5" customHeight="1" spans="1:7">
       <c r="A7" s="5"/>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="6">
         <v>1</v>
       </c>
-      <c r="C7" s="6" t="str">
-        <v>临时守卫套装</v>
-      </c>
-      <c r="D7" s="6" t="n">
+      <c r="C7" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="6">
         <v>2</v>
       </c>
-      <c r="E7" s="6" t="str">
-        <v>攻击比例</v>
-      </c>
-      <c r="F7" s="6" t="str">
+      <c r="E7" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" s="6">
         <v>0.05</v>
       </c>
       <c r="G7" s="6"/>
     </row>
-    <row r="8" ht="16.5" customHeight="1">
-      <c r="B8" t="n" s="6">
+    <row r="8" ht="16.5" customHeight="1" spans="1:7">
+      <c r="B8" s="6">
         <v>2</v>
       </c>
-      <c r="C8" t="str" s="6">
-        <v>临时守卫套装</v>
-      </c>
-      <c r="D8" t="n" s="6">
+      <c r="C8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="6">
         <v>4</v>
       </c>
-      <c r="E8" t="str" s="6">
-        <v>防御比例</v>
-      </c>
-      <c r="F8" t="str" s="6">
+      <c r="E8" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="6">
         <v>0.05</v>
       </c>
       <c r="G8" s="6"/>
